--- a/Tables/TableS1_FromR.xlsx
+++ b/Tables/TableS1_FromR.xlsx
@@ -351,50 +351,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Term</t>
+          <t>Pair</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>Number of nodules</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>F value</t>
+          <t>% Mucoid</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pr(&gt;F)</t>
+          <t>% Dry</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% Mixture</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Morphology</t>
+          <t>091_101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4668.265</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>38.224</t>
+          <t>68.966</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>22.414</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8.621</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>015_099</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>36.538</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>46.154</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>17.308</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>016_100</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>49.231</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>33.846</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16.923</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>029_098</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>18.000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56.000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>26.000</t>
         </is>
       </c>
     </row>
